--- a/Assets/GameSample/Forms/Excels/Story/Event/GameCmdTypeData_CmdTypeData.xlsx
+++ b/Assets/GameSample/Forms/Excels/Story/Event/GameCmdTypeData_CmdTypeData.xlsx
@@ -1241,8 +1241,16 @@
       <c r="E16" s="3"/>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="2"/>
-      <c r="B17" s="3"/>
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>10012</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>mission</t>
+        </is>
+      </c>
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
